--- a/synthetic/documents/xlsx/order_084_SW-01083.xlsx
+++ b/synthetic/documents/xlsx/order_084_SW-01083.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SafeWork Solutions Inc. (SYNTHETIC)</t>
+          <t>Nova Company (SYNTHETIC)</t>
         </is>
       </c>
     </row>
@@ -495,7 +495,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06-23-2026</t>
+          <t>07-01-2026</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Indianapolis Warehouse</t>
+          <t>Nova Shipping Location 1</t>
         </is>
       </c>
     </row>
@@ -554,27 +554,27 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>SWS-PPE-1804</t>
+          <t>JAN-FFN-064</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Face Shield clear 8x15.5 inch</t>
+          <t>Floor Finish High Gloss (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>4.5</v>
+        <v>70.67</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>22.5</v>
+        <v>706.7</v>
       </c>
     </row>
     <row r="10">
@@ -583,27 +583,27 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>SWS-JS-4927</t>
+          <t>FST-FWS-34-10</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Roll Paper Towels Brown 1-ply</t>
+          <t>Flat Washer 3/4-10 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>31.27</v>
+        <v>13.79</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>312.7</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -612,27 +612,27 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>FST-HCS-51618-1-G5Z-B25</t>
+          <t>JAN-LNR-4046-07-WH</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Hex Cap Screw 5/16-18 x 1" Grade 5 Zinc</t>
+          <t>Can Liner 40x46 0.7mil White Roll (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13.59</v>
+        <v>33.18</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>67.95</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="12">
@@ -641,27 +641,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>FST-HCS-3816-112-G5Z-B50</t>
+          <t>TLS-UTK-113</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Hex Cap Screw 3/8-16 x 1-1/2" Grade 5 Zinc</t>
+          <t>Utility Knife Retractable (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.66</v>
+        <v>6.3</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>231.84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -670,27 +670,27 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SWS-ABR-6633</t>
+          <t>NOVA-LUB-2941</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Sanding Disc 5 inch hook &amp; loop 80 grit</t>
+          <t>Multi-Purpose Grease (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>31.22</v>
+        <v>113.57</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>749.28</v>
+        <v>227.14</v>
       </c>
     </row>
     <row r="14">
@@ -699,16 +699,16 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>TAP-PT-2-CLR</t>
+          <t>NOVA-JAN-0114</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Packing Tape Clear 2 inch x 110 yd</t>
+          <t>Facial Tissue Flat Box (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>68.72</v>
+        <v>46.07</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>687.2</v>
+        <v>552.84</v>
       </c>
     </row>
     <row r="15">
@@ -728,16 +728,16 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SWS-JS-4985</t>
+          <t>JAN-DSP-185</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 43x47 0.5mil Clear 500/CS</t>
+          <t>Disinfectant Spray (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -745,10 +745,10 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>47.61</v>
+        <v>61.81</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>238.05</v>
+        <v>185.43</v>
       </c>
     </row>
     <row r="16">
@@ -757,27 +757,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>SWS-JS-5167</t>
+          <t>NOVA-TOO-3144</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Toilet Paper 2-ply standard roll</t>
+          <t>Tape Measure 25ft (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D16" s="4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>34.46</v>
+        <v>21.99</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>206.76</v>
+        <v>21.99</v>
       </c>
     </row>
   </sheetData>

--- a/synthetic/documents/xlsx/order_084_SW-01083.xlsx
+++ b/synthetic/documents/xlsx/order_084_SW-01083.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Purchase Order" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -511,204 +511,187 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Delivery Date:</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Item Code</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>UoM</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>Unit Price</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>JAN-FFN-064</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Floor Finish High Gloss (SYNTHETIC)</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>CS</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>70.67</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>706.7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>FST-FWS-34-10</t>
+          <t>JAN-FFN-064</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Flat Washer 3/4-10 Zinc (SYNTHETIC)</t>
+          <t>Floor Finish High Gloss (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>CS</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>13.79</v>
+        <v>70.67</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>82.73999999999999</v>
+        <v>706.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>JAN-LNR-4046-07-WH</t>
+          <t>FST-FWS-34-10</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Can Liner 40x46 0.7mil White Roll (SYNTHETIC)</t>
+          <t>Flat Washer 3/4-10 Zinc (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>33.18</v>
+        <v>13.79</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>66.36</v>
+        <v>82.73999999999999</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>TLS-UTK-113</t>
+          <t>JAN-LNR-4046-07-WH</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Utility Knife Retractable (SYNTHETIC)</t>
+          <t>Can Liner 40x46 0.7mil White Roll (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>EA</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6.3</v>
+        <v>33.18</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>63</v>
+        <v>66.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>NOVA-LUB-2941</t>
+          <t>TLS-UTK-113</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Multi-Purpose Grease (SYNTHETIC)</t>
+          <t>Utility Knife Retractable (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CS</t>
+          <t>EA</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>113.57</v>
+        <v>6.3</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>227.14</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>NOVA-JAN-0114</t>
+          <t>NOVA-LUB-2941</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Facial Tissue Flat Box (SYNTHETIC)</t>
+          <t>Multi-Purpose Grease (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
@@ -716,28 +699,28 @@
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>46.07</v>
+        <v>113.57</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>552.84</v>
+        <v>227.14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>JAN-DSP-185</t>
+          <t>NOVA-JAN-0114</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Disinfectant Spray (SYNTHETIC)</t>
+          <t>Facial Tissue Flat Box (SYNTHETIC)</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -745,38 +728,67 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>61.81</v>
+        <v>46.07</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>185.43</v>
+        <v>552.84</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>JAN-DSP-185</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Disinfectant Spray (SYNTHETIC)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>CS</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>185.43</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>NOVA-TOO-3144</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Tape Measure 25ft (SYNTHETIC)</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>EA</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F17" s="4" t="n">
         <v>21.99</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G17" s="4" t="n">
         <v>21.99</v>
       </c>
     </row>
